--- a/crates/snapsheet/tests/fixtures/invalid_attribute.xlsx
+++ b/crates/snapsheet/tests/fixtures/invalid_attribute.xlsx
@@ -117,17 +117,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>FIELD</t>
+          <t>REG_DESC</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>BIT</t>
+          <t>FIELD</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>WIDTH</t>
+          <t>BIT</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -142,7 +142,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>DESCRIPTION</t>
+          <t>FIELD_DESC</t>
         </is>
       </c>
     </row>
@@ -157,19 +157,14 @@
           <t>reg</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>[31:0]</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/crates/snapsheet/tests/fixtures/invalid_attribute.xlsx
+++ b/crates/snapsheet/tests/fixtures/invalid_attribute.xlsx
@@ -132,12 +132,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ATTRIBUTE</t>
+          <t>ATTR</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>RESET</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
